--- a/d/2026-09-08_会员有效性分析.xlsx
+++ b/d/2026-09-08_会员有效性分析.xlsx
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C3" t="n">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D3" t="n">
         <v>54</v>
       </c>
       <c r="E3" t="n">
-        <v>95.01000000000001</v>
+        <v>95.02</v>
       </c>
       <c r="F3" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="4">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="C4" t="n">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="D4" t="n">
         <v>48</v>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>764</v>
+      </c>
+      <c r="C7" t="n">
         <v>763</v>
-      </c>
-      <c r="C7" t="n">
-        <v>762</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -709,16 +709,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
         <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>31.25</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="4">
@@ -2018,19 +2018,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DJI北京翠微百货授权体验店</t>
+          <t>华为北京长楹龙湖</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E52" t="n">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2045,19 +2045,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DJI上海FFC滨江悦里授权体验店</t>
+          <t>DJI北京翠微百货授权体验店</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E53" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2072,19 +2072,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DJI北京丽泽天街授权体验店</t>
+          <t>DJI上海FFC滨江悦里授权体验店</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="E54" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2099,19 +2099,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>APR北京大兴龙湖</t>
+          <t>DJI北京丽泽天街授权体验店</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="E55" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2126,19 +2126,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DJI上海徐汇万科广场授权体验店</t>
+          <t>APR北京大兴龙湖</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E56" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2153,19 +2153,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>华为福州中骏世界城</t>
+          <t>DJI上海徐汇万科广场授权体验店</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="E57" t="n">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>华为福州五四北泰禾广场</t>
+          <t>华为福州中骏世界城</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E58" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2207,19 +2207,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DJI北京东坝万达广场授权体验店</t>
+          <t>华为福州五四北泰禾广场</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="E59" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>APR北京昌发展万科</t>
+          <t>DJI北京东坝万达广场授权体验店</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E60" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2261,19 +2261,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>APR北京昌发展万科</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E61" t="n">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2288,19 +2288,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>APR北京东坝万达</t>
+          <t>APR成都双楠伊藤</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E62" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>华为福州平潭吾悦</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="E63" t="n">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -2342,19 +2342,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DJI北京西北旺万象汇授权体验店</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E64" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2369,19 +2369,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>APR北京西铁营万达</t>
+          <t>华为福州平潭吾悦</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E65" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2396,19 +2396,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DJI上海虹口凯德授权体验店</t>
+          <t>DJI北京西北旺万象汇授权体验店</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E66" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -2423,19 +2423,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>APR成都双楠伊藤</t>
+          <t>APR北京西铁营万达</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E67" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2450,19 +2450,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>华为泉州石狮泰禾广场</t>
+          <t>DJI上海虹口凯德授权体验店</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E68" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2477,19 +2477,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DJI北京龙湖大兴天街授权体验店</t>
+          <t>华为泉州石狮泰禾广场</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E69" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2504,19 +2504,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>APR成都金楠天街</t>
+          <t>DJI北京龙湖大兴天街授权体验店</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E70" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -2531,19 +2531,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>华为北京酒仙桥颐堤港</t>
+          <t>APR成都金楠天街</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E71" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2558,19 +2558,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>华为北京酒仙桥颐堤港</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E72" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -2585,19 +2585,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>APR北京回龙观华联</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2612,19 +2612,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>APR北京回龙观华联</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="E74" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -2639,19 +2639,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>APR北京颐堤港</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="E75" t="n">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2666,19 +2666,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>APR北京颐堤港</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E76" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DJI北京龙湖房山天街授权体验店</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -2720,19 +2720,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>DJI北京龙湖房山天街授权体验店</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E78" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2747,19 +2747,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E79" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2774,19 +2774,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>APR北京西三旗万象汇</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E80" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2801,19 +2801,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>APR成都高新伊藤</t>
+          <t>APR北京西三旗万象汇</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E81" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2828,19 +2828,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>APR北京同成街华联</t>
+          <t>APR成都高新伊藤</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E82" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>APR北京同成街华联</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="E83" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>华为北京通州乐堤港</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E84" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>华为北京怀柔万达</t>
+          <t>华为北京通州乐堤港</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E85" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>华为北京长楹龙湖</t>
+          <t>华为北京怀柔万达</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="E86" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>132****8571</t>
+          <t>152****4333</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京大兴大族</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>150****2535</t>
+          <t>136****0516</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5573,7 +5573,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>138****9886</t>
+          <t>185****5730</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5596,7 +5596,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>185****5730</t>
+          <t>136****4066</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5619,7 +5619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>135****6745</t>
+          <t>138****9886</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5642,7 +5642,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>152****4333</t>
+          <t>132****8571</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5665,7 +5665,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>136****0516</t>
+          <t>133****5880</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5688,7 +5688,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>185****7000</t>
+          <t>135****6745</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5711,7 +5711,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>158****5701</t>
+          <t>150****2535</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5722,19 +5722,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>APR北京怀柔万达</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>136****4066</t>
+          <t>183****2985</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>192****7511</t>
+          <t>185****7000</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京丰科万达</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5780,7 +5780,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>133****5880</t>
+          <t>158****5701</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5791,19 +5791,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>APR北京怀柔万达</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>183****2985</t>
+          <t>192****7511</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>132****8571</t>
+          <t>150****2535</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>150****2535</t>
+          <t>132****8571</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -15786,12 +15786,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6942103183102</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -15896,12 +15896,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183102</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -15951,12 +15951,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -16006,12 +16006,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -16061,12 +16061,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -16281,12 +16281,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -16446,12 +16446,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -16501,12 +16501,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -16666,12 +16666,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -16776,12 +16776,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -16831,12 +16831,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -17051,12 +17051,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -17106,12 +17106,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -17161,12 +17161,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -17271,12 +17271,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -17326,12 +17326,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -17381,12 +17381,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -17601,12 +17601,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -17711,12 +17711,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -17766,12 +17766,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -17821,12 +17821,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -17876,12 +17876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -17931,12 +17931,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -18151,12 +18151,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -18261,12 +18261,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -18426,12 +18426,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -18536,12 +18536,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -18591,12 +18591,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -18646,12 +18646,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -18701,12 +18701,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -18811,12 +18811,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -18866,12 +18866,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -18921,12 +18921,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -18976,12 +18976,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -19031,12 +19031,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -19196,12 +19196,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -19251,12 +19251,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -19361,12 +19361,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -19471,12 +19471,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -19526,12 +19526,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -19636,12 +19636,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -19746,12 +19746,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -19801,12 +19801,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -19966,12 +19966,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -20021,12 +20021,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -20186,12 +20186,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -20241,12 +20241,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -20461,12 +20461,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -20516,12 +20516,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -20736,12 +20736,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20956,12 +20956,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21066,12 +21066,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -21121,12 +21121,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -21231,12 +21231,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -21286,12 +21286,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -21341,12 +21341,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -21451,12 +21451,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -21726,12 +21726,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -21781,12 +21781,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -21836,12 +21836,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -21891,12 +21891,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -22166,12 +22166,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -22276,12 +22276,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -22331,12 +22331,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -22386,12 +22386,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -22441,12 +22441,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -22551,12 +22551,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -22606,12 +22606,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -22826,12 +22826,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -22881,12 +22881,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -22936,12 +22936,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -22991,12 +22991,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -23101,12 +23101,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -23156,12 +23156,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -23376,12 +23376,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K140" t="n">
@@ -23431,12 +23431,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -23486,12 +23486,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -23651,12 +23651,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -23816,12 +23816,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -23926,12 +23926,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -23981,12 +23981,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -24036,12 +24036,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -24201,12 +24201,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -24256,12 +24256,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -24311,12 +24311,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -24421,12 +24421,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K159" t="n">
@@ -24476,12 +24476,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K160" t="n">
@@ -24531,12 +24531,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K161" t="n">
@@ -24586,12 +24586,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -24641,12 +24641,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K163" t="n">
@@ -24696,12 +24696,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K164" t="n">
@@ -24806,12 +24806,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K166" t="n">
@@ -24916,12 +24916,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K168" t="n">
@@ -24971,12 +24971,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K169" t="n">
@@ -25301,12 +25301,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -25576,12 +25576,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K180" t="n">
@@ -25631,12 +25631,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K181" t="n">
@@ -25741,12 +25741,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K183" t="n">
@@ -25796,12 +25796,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K184" t="n">
@@ -26016,12 +26016,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K188" t="n">
@@ -26071,12 +26071,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K189" t="n">
@@ -26126,12 +26126,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K190" t="n">
@@ -26181,12 +26181,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K191" t="n">
@@ -26566,12 +26566,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K198" t="n">
@@ -26621,12 +26621,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K199" t="n">
@@ -26676,12 +26676,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K200" t="n">
@@ -26731,12 +26731,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K201" t="n">
@@ -26786,12 +26786,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -26841,12 +26841,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K203" t="n">
@@ -26896,12 +26896,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K204" t="n">
@@ -27061,12 +27061,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -27171,12 +27171,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K209" t="n">
@@ -27226,12 +27226,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K210" t="n">
@@ -27336,12 +27336,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -27446,12 +27446,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K214" t="n">
@@ -27501,12 +27501,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K215" t="n">
@@ -27666,12 +27666,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K218" t="n">
@@ -27881,17 +27881,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>MateBook Pro S</t>
+          <t>Hi MateBook</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>MateBook Pro S MOR-M1(HarmonyOS 24GB+512GB)触屏 仲夏紫</t>
+          <t>Hi Matebook 14 MNCAC-32(AMD Radeon AMD Ryzen 7 Win11 24GB+1TB)触屏 极夜灰</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>6942711313007</t>
+          <t>6975503504697</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -27936,17 +27936,17 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Hi MateBook</t>
+          <t>MateBook Pro S</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Hi Matebook 14 MNCAC-32(AMD Radeon AMD Ryzen 7 Win11 24GB+1TB)触屏 极夜灰</t>
+          <t>MateBook Pro S MOR-M1(HarmonyOS 24GB+512GB)触屏 仲夏紫</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>6975503504697</t>
+          <t>6942711313007</t>
         </is>
       </c>
       <c r="K223" t="n">
@@ -28271,12 +28271,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K229" t="n">
@@ -28326,12 +28326,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K230" t="n">
@@ -28436,12 +28436,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K232" t="n">
@@ -28491,12 +28491,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K233" t="n">
@@ -28546,12 +28546,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K234" t="n">
@@ -28601,12 +28601,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K235" t="n">
@@ -28656,12 +28656,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K236" t="n">
@@ -28766,12 +28766,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K238" t="n">
@@ -28821,12 +28821,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K239" t="n">
@@ -28876,12 +28876,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K240" t="n">
@@ -28931,12 +28931,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K241" t="n">
@@ -29096,12 +29096,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Mate 80 VYG-AL30(12GB+512GB) 晨曦金</t>
+          <t>Mate 80 VYG-AL30(12GB+512GB) 云杉绿</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>6942103191657</t>
+          <t>6942103191640</t>
         </is>
       </c>
       <c r="K244" t="n">
@@ -29151,12 +29151,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Mate 80 VYG-AL30(12GB+512GB) 云杉绿</t>
+          <t>Mate 80 VYG-AL30(12GB+512GB) 晨曦金</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>6942103191640</t>
+          <t>6942103191657</t>
         </is>
       </c>
       <c r="K245" t="n">
@@ -30546,12 +30546,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -30617,12 +30617,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -30759,12 +30759,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>195****64870</t>
+          <t>195****64757</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -30830,12 +30830,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>195****64757</t>
+          <t>195****64870</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -30901,12 +30901,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -30972,12 +30972,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -31109,17 +31109,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>鼠标和键盘</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 清薄键盘保护膜</t>
+          <t>ZUER卓耳 四向滚轮三模无线鼠标</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6922329934702</t>
+          <t>6973620631524</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -31180,17 +31180,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>TOMTOC Defender A14 城市简约手提电脑包</t>
+          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6970412220850</t>
+          <t>6946333017596</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -31251,17 +31251,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
+          <t>TOMTOC Defender A14 城市简约手提电脑包</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6946333017596</t>
+          <t>6970412220850</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -31322,17 +31322,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>鼠标和键盘</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ZUER卓耳 四向滚轮三模无线鼠标</t>
+          <t>VOKAMO沃咔曼 清薄键盘保护膜</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6973620631524</t>
+          <t>6922329934702</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -31393,17 +31393,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ZGA 米兰尼斯金属磁吸表带 Watch 38/40/41mm 黑色</t>
+          <t>COMMA珂玛  盾威系列全屏 Apple Watch 42mm 保护膜 V3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6927123804657</t>
+          <t>6942297146396</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -31464,17 +31464,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>表带</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>COMMA珂玛  盾威系列全屏 Apple Watch 42mm 保护膜 V3</t>
+          <t>ZGA 米兰尼斯金属磁吸表带 Watch 38/40/41mm 黑色</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>6942297146396</t>
+          <t>6927123804657</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -31535,17 +31535,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6922329935952</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -31606,17 +31606,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6922329935921</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -31682,12 +31682,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6955482542736</t>
+          <t>6955482539514</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -31748,17 +31748,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6922329935587</t>
+          <t>6955482542736</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -31890,17 +31890,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
+          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6955482539514</t>
+          <t>6922329935921</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -31966,12 +31966,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
+          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6922329935952</t>
+          <t>6922329935587</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -32032,17 +32032,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>iPad Pro</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11 英寸 iPad Pro 无线局域网机型 256GB 配标准玻璃面板 - 银色</t>
+          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>195****95549</t>
+          <t>6937045847984</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -32174,17 +32174,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPad Pro</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>11 英寸 iPad Pro 无线局域网机型 256GB 配标准玻璃面板 - 银色</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6927123805548</t>
+          <t>195****95549</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -32245,17 +32245,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6927123805548</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -32316,17 +32316,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -32387,17 +32387,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6937045847984</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -32529,17 +32529,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6922329935303</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -32600,17 +32600,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -32671,17 +32671,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -32747,12 +32747,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6922329935303</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -33173,12 +33173,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6941876245444</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -33244,12 +33244,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>6941876245444</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -33386,12 +33386,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
+          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4894222083837</t>
+          <t>6927123810382</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -33452,17 +33452,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -33528,12 +33528,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>4894222083837</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -33594,17 +33594,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6927123810382</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -37416,17 +37416,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -37487,17 +37487,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -37558,17 +37558,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -37629,17 +37629,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -37705,12 +37705,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 黑色 iPhone 17</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123810429</t>
         </is>
       </c>
       <c r="L103" t="n">
@@ -37771,17 +37771,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -37842,17 +37842,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 黑色 iPhone 17</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>6927123810429</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L105" t="n">
@@ -38410,17 +38410,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -38481,17 +38481,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>SWITCHEASYiPhone 系列 LenStand M 镜头支架防摔保护壳珊瑚 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>4895241136474</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -38623,17 +38623,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>SWITCHEASYiPhone 系列 LenStand M 镜头支架防摔保护壳珊瑚 iPhone 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>4895241136474</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -38699,12 +38699,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线 橙色</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>6955482530214</t>
+          <t>6922329936645</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -38770,12 +38770,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线 橙色</t>
+          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>6922329936645</t>
+          <t>6955482530214</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -38836,17 +38836,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -39191,17 +39191,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -39262,17 +39262,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -39338,12 +39338,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -39409,12 +39409,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -39475,17 +39475,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -39546,17 +39546,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -39617,17 +39617,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -39688,17 +39688,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -39759,17 +39759,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -39906,12 +39906,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -40545,12 +40545,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -40682,17 +40682,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
+          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>195****28869</t>
+          <t>XMPZ202612189</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -40753,17 +40753,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
+          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>XMPZ202612189</t>
+          <t>195****28869</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -41179,23 +41179,20 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPad基础版</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>NO1BOX IPhone 17 Pro Max 蜡笔小新春日部防卫队保护壳 出发啦</t>
+          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>6923517323407</t>
+          <t>195****86379</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="n">
         <v>1</v>
       </c>
       <c r="N152" t="n">
@@ -41318,20 +41315,23 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>iPad基础版</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
+          <t>NO1BOX IPhone 17 Pro Max 蜡笔小新春日部防卫队保护壳 出发啦</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>195****86379</t>
+          <t>6923517323407</t>
         </is>
       </c>
       <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
         <v>1</v>
       </c>
       <c r="N154" t="n">
@@ -41454,17 +41454,17 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>LIBRATONE小鸟音响 UP 耳机 莺眉黄</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>6942297127005</t>
+          <t>6975324441119</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -41530,12 +41530,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动保护皮套带笔槽  11 英寸 iPad (A16) 动物派对</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>6942297127241</t>
+          <t>6942297127005</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -41596,17 +41596,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>LIBRATONE小鸟音响 UP 耳机 莺眉黄</t>
+          <t>COMMA珂玛 iPad 灵动保护皮套带笔槽  11 英寸 iPad (A16) 动物派对</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>6975324441119</t>
+          <t>6942297127241</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -41743,12 +41743,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6942297127012</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -41814,12 +41814,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>6942297127012</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -42022,17 +42022,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>音乐</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
+          <t>AirPods 4 (支持主动降噪)-MXP93CH/A</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>6941876245437</t>
+          <t>195****89550</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -42093,17 +42093,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>音乐</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>AirPods 4 (支持主动降噪)-MXP93CH/A</t>
+          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>195****89550</t>
+          <t>6941876245437</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -45632,17 +45632,17 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>外设</t>
+          <t>保护</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>迈多多 DY24 10000mAh移动电源 白色（电商）</t>
+          <t>仁清 UV高清晶钻膜 180GJZ-01G9是（S码）</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>6927123806422</t>
+          <t>6941402717384</t>
         </is>
       </c>
       <c r="L215" t="n">
@@ -45703,17 +45703,17 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>保护</t>
+          <t>外设</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>仁清 UV高清晶钻膜 180GJZ-01G9是（S码）</t>
+          <t>迈多多 DY24 10000mAh移动电源 白色（电商）</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>6941402717384</t>
+          <t>6927123806422</t>
         </is>
       </c>
       <c r="L216" t="n">
@@ -46205,12 +46205,12 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L223" t="n">
@@ -46271,17 +46271,17 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L224" t="n">
@@ -46342,17 +46342,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>6927123810436</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L225" t="n">
@@ -46413,17 +46413,17 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L226" t="n">
@@ -46484,17 +46484,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L227" t="n">
@@ -46555,17 +46555,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6927123810436</t>
         </is>
       </c>
       <c r="L228" t="n">
@@ -46626,17 +46626,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L229" t="n">
@@ -47123,17 +47123,17 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L236" t="n">
@@ -47194,17 +47194,17 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L237" t="n">
@@ -47478,17 +47478,17 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>6974623613029</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L241" t="n">
@@ -47554,12 +47554,12 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>4894222083820</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L242" t="n">
@@ -47620,17 +47620,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L243" t="n">
@@ -47691,17 +47691,17 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>6941876245437</t>
+          <t>6928288500057</t>
         </is>
       </c>
       <c r="L244" t="n">
@@ -47762,17 +47762,17 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
+          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>6928288500057</t>
+          <t>6974623613029</t>
         </is>
       </c>
       <c r="L245" t="n">
@@ -47833,17 +47833,17 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6941876245437</t>
         </is>
       </c>
       <c r="L246" t="n">
@@ -47909,12 +47909,12 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 黑色</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>4894222083820</t>
         </is>
       </c>
       <c r="L247" t="n">
@@ -48488,6 +48488,9 @@
       <c r="L255" t="n">
         <v>1</v>
       </c>
+      <c r="M255" t="n">
+        <v>1</v>
+      </c>
       <c r="N255" t="n">
         <v>8235</v>
       </c>
@@ -48545,12 +48548,12 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Osmo 迷你三脚架</t>
+          <t>Osmo Pocket 4P 标准套装</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>6941565969811</t>
+          <t>6937224148321</t>
         </is>
       </c>
       <c r="L256" t="n">
@@ -48613,18 +48616,15 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
+          <t>Osmo 迷你三脚架</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>6937224151062</t>
+          <t>6941565969811</t>
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1</v>
-      </c>
-      <c r="M257" t="n">
         <v>1</v>
       </c>
       <c r="N257" t="n">
@@ -48752,18 +48752,15 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Osmo Pocket 4P 标准套装</t>
+          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>6937224148321</t>
+          <t>6937224151062</t>
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1</v>
-      </c>
-      <c r="M259" t="n">
         <v>1</v>
       </c>
       <c r="N259" t="n">
@@ -48834,6 +48831,9 @@
       <c r="L260" t="n">
         <v>1</v>
       </c>
+      <c r="M260" t="n">
+        <v>1</v>
+      </c>
       <c r="N260" t="n">
         <v>8235</v>
       </c>
@@ -51160,12 +51160,12 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 黑色</t>
+          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 白色</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>6941487218028</t>
+          <t>6941487218011</t>
         </is>
       </c>
       <c r="L293" t="n">
@@ -51515,12 +51515,12 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 白色</t>
+          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 黑色</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>6941487218011</t>
+          <t>6941487218028</t>
         </is>
       </c>
       <c r="L298" t="n">
@@ -52859,12 +52859,12 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L317" t="n">
@@ -52930,12 +52930,12 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L318" t="n">
@@ -53138,17 +53138,17 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>SWITCHEASY Apple Watch 系列 Mesh 不锈钢磁扣表带</t>
+          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>6977503191334</t>
+          <t>6942297146426</t>
         </is>
       </c>
       <c r="L321" t="n">
@@ -53209,17 +53209,17 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>表带</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
+          <t>SWITCHEASY Apple Watch 系列 Mesh 不锈钢磁扣表带</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>6942297146426</t>
+          <t>6977503191334</t>
         </is>
       </c>
       <c r="L322" t="n">
@@ -53285,12 +53285,12 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA iPhone 17e 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123814069</t>
         </is>
       </c>
       <c r="L323" t="n">
@@ -53351,17 +53351,17 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17e 二强防静电高清钢化膜 透明</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>6927123814069</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L324" t="n">
@@ -53427,12 +53427,12 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>ZGA 明透磁吸 保护壳 透明 iPhone 16e</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>6927123805746</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L325" t="n">
@@ -53493,17 +53493,17 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>ZGA 明透磁吸 保护壳 透明 iPhone 16e</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6927123805746</t>
         </is>
       </c>
       <c r="L326" t="n">
@@ -53990,17 +53990,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>LIBRATONE小鸟音响 UP 耳机 莺眉黄</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>6975324441119</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L333" t="n">
@@ -54066,12 +54066,12 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>VOKAMO沃咔曼 iPad Air 魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6922329934283</t>
         </is>
       </c>
       <c r="L334" t="n">
@@ -54132,17 +54132,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>LIBRATONE小鸟音响 UP 耳机 莺眉黄</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6975324441119</t>
         </is>
       </c>
       <c r="L335" t="n">
@@ -54208,12 +54208,12 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad Air 魔幻旋转防刮保护套</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>6922329934283</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L336" t="n">
@@ -54558,17 +54558,17 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L341" t="n">
@@ -54629,17 +54629,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L342" t="n">
@@ -54978,17 +54978,17 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo 70 厘米隐形自拍杆</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224111165</t>
         </is>
       </c>
       <c r="L347" t="n">
@@ -55049,17 +55049,17 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Osmo 70 厘米隐形自拍杆</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>6937224111165</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L348" t="n">
@@ -59285,17 +59285,17 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>运营商卡号</t>
+          <t>MatePad pro</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>橙分期团购合约-129-24（终端直降1170）</t>
+          <t>MatePad Pro 12.2寸 MRO-W00(12GB+512GB) 砚黑</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>811094496</t>
+          <t>6942103130816</t>
         </is>
       </c>
       <c r="L408" t="n">
@@ -59356,17 +59356,17 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>MatePad pro</t>
+          <t>运营商卡号</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>MatePad Pro 12.2寸 MRO-W00(12GB+512GB) 砚黑</t>
+          <t>橙分期团购合约-129-24（终端直降1170）</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>6942103130816</t>
+          <t>811094496</t>
         </is>
       </c>
       <c r="L409" t="n">
@@ -60699,17 +60699,17 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>iPad Pro</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>11 英寸 iPad Pro 无线局域网 + 蜂窝网络机型 256GB 配标准玻璃面板 - 深空黑色 - ME6E4CH/A</t>
+          <t>ZGA iPad 流派系列 Y 折 保护皮套</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>195****03541</t>
+          <t>6927123806750</t>
         </is>
       </c>
       <c r="L428" t="n">
@@ -60841,17 +60841,17 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L430" t="n">
@@ -60983,17 +60983,17 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L432" t="n">
@@ -61054,17 +61054,17 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPad Pro</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>ZGA iPad 流派系列 Y 折 保护皮套</t>
+          <t>11 英寸 iPad Pro 无线局域网 + 蜂窝网络机型 256GB 配标准玻璃面板 - 深空黑色 - ME6E4CH/A</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>6927123806750</t>
+          <t>195****03541</t>
         </is>
       </c>
       <c r="L433" t="n">
@@ -62616,17 +62616,17 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>6927123805432</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L455" t="n">
@@ -62687,17 +62687,17 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L456" t="n">
@@ -62834,12 +62834,12 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6927123805432</t>
         </is>
       </c>
       <c r="L458" t="n">
@@ -63113,17 +63113,17 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>RICHIC锐壳 iPhone 17 Pro Max 透明磨砂保护壳 透明</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6978880670153</t>
         </is>
       </c>
       <c r="L462" t="n">
@@ -63189,12 +63189,12 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 Pro Max 迪士尼莓果草莓熊磁吸保护壳 粉色</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>6975749267219</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L463" t="n">
@@ -63255,17 +63255,17 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 白色</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>6928288555361</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L464" t="n">
@@ -63331,12 +63331,12 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPhone 17 Pro Max 透明磨砂保护壳 透明</t>
+          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 Pro Max 迪士尼莓果草莓熊磁吸保护壳 粉色</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>6978880670153</t>
+          <t>6975749267219</t>
         </is>
       </c>
       <c r="L465" t="n">
@@ -63397,17 +63397,17 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 白色</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>6941876245444</t>
+          <t>6928288555361</t>
         </is>
       </c>
       <c r="L466" t="n">
@@ -63468,17 +63468,17 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>6941876245444</t>
         </is>
       </c>
       <c r="L467" t="n">
@@ -63539,17 +63539,17 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L468" t="n">
@@ -63681,17 +63681,17 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 512GB 星宇橙色 - MG8X4CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>195****28906</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L470" t="n">
@@ -63752,17 +63752,17 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro 512GB 星宇橙色 - MG8X4CH/A</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****28906</t>
         </is>
       </c>
       <c r="L471" t="n">
@@ -64107,17 +64107,17 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>SOUNDCORE声阔 Life Q45 无线蓝牙耳机头戴式降噪耳机</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>6940268897810</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L476" t="n">
@@ -64178,17 +64178,17 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>SOUNDCORE声阔 Life Q45 无线蓝牙耳机头戴式降噪耳机</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>6940268897810</t>
         </is>
       </c>
       <c r="L477" t="n">
@@ -72620,12 +72620,12 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>仁清 UV高清晶钻膜 180GJZ-01G9是（S码）</t>
+          <t>TimeLock Mate 80/80 Pro 3D 康宁高清全屏 钢化膜</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
         <is>
-          <t>6941402717384</t>
+          <t>6979434900252</t>
         </is>
       </c>
       <c r="L596" t="n">
@@ -72691,12 +72691,12 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>TimeLock Mate 80/80 Pro 3D 康宁高清全屏 钢化膜</t>
+          <t>仁清 UV高清晶钻膜 180GJZ-01G9是（S码）</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
         <is>
-          <t>6979434900252</t>
+          <t>6941402717384</t>
         </is>
       </c>
       <c r="L597" t="n">
@@ -72899,17 +72899,17 @@
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>畅享 90</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>礼品-通用-随行杯-银棕色</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>A0800803</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="L600" t="n">
@@ -72970,17 +72970,17 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>畅享 90</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>礼品-通用-随行杯-银棕色</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>A0800803</t>
         </is>
       </c>
       <c r="L601" t="n">
@@ -73472,12 +73472,12 @@
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K608" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L608" t="n">
@@ -73538,17 +73538,17 @@
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17 Pro</t>
+          <t>iPhone 17 Pro 512GB 星宇橙色 - MG8X4CH/A</t>
         </is>
       </c>
       <c r="K609" t="inlineStr">
         <is>
-          <t>6927123810498</t>
+          <t>195****28906</t>
         </is>
       </c>
       <c r="L609" t="n">
@@ -73609,17 +73609,17 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 512GB 星宇橙色 - MG8X4CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>195****28906</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L610" t="n">
@@ -73680,17 +73680,17 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>存储</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>RECCI锐思 RPB W27 10000mAh 银河快充移动电源</t>
+          <t>LEXAR雷克沙 Professional Go 手机固态硬盘 银色 1T</t>
         </is>
       </c>
       <c r="K611" t="inlineStr">
         <is>
-          <t>6955482535158</t>
+          <t>6977105652165</t>
         </is>
       </c>
       <c r="L611" t="n">
@@ -73751,17 +73751,17 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>存储</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>LEXAR雷克沙 Professional Go 手机固态硬盘 银色 1T</t>
+          <t>RECCI锐思 RPB W27 10000mAh 银河快充移动电源</t>
         </is>
       </c>
       <c r="K612" t="inlineStr">
         <is>
-          <t>6977105652165</t>
+          <t>6955482535158</t>
         </is>
       </c>
       <c r="L612" t="n">
@@ -73822,17 +73822,17 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K613" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L613" t="n">
@@ -73893,17 +73893,17 @@
       </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>AppleCare Services for iPhone 17 Pro - SY7N2CH/A</t>
         </is>
       </c>
       <c r="K614" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>195****10120</t>
         </is>
       </c>
       <c r="L614" t="n">
@@ -74035,17 +74035,17 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro - SY7N2CH/A</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>195****10120</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L616" t="n">
@@ -74111,12 +74111,12 @@
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17 Pro</t>
         </is>
       </c>
       <c r="K617" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6927123810498</t>
         </is>
       </c>
       <c r="L617" t="n">
@@ -74390,17 +74390,17 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L621" t="n">
@@ -74532,17 +74532,17 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>MOCOLL摩可 iPad Air 11英寸 铂金系列 高清钢化玻璃膜</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6937045848004</t>
         </is>
       </c>
       <c r="L623" t="n">
@@ -74674,17 +74674,17 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 iPad Air 11英寸 铂金系列 高清钢化玻璃膜</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>6937045848004</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L625" t="n">
@@ -75242,17 +75242,17 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L633" t="n">
@@ -75389,12 +75389,12 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6927123810511</t>
         </is>
       </c>
       <c r="L635" t="n">
@@ -75455,17 +75455,17 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>6927123810511</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L636" t="n">
@@ -75526,17 +75526,17 @@
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>存储</t>
         </is>
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>LEXAR雷克沙 SL500 高速移动固态硬盘磁吸套装 1TB</t>
         </is>
       </c>
       <c r="K637" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6977105651717</t>
         </is>
       </c>
       <c r="L637" t="n">
@@ -75594,17 +75594,17 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>存储</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>LEXAR雷克沙 SL500 高速移动固态硬盘磁吸套装 1TB</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>6977105651717</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L638" t="n">
@@ -75662,23 +75662,20 @@
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MP39 10000mAh 传奇二代磁吸快充移动电源</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>6955482532911</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L639" t="n">
-        <v>1</v>
-      </c>
-      <c r="M639" t="n">
         <v>1</v>
       </c>
       <c r="N639" t="n">
@@ -75733,17 +75730,17 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L640" t="n">
@@ -75806,15 +75803,18 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>MAXCO美能格 MP39 10000mAh 传奇二代磁吸快充移动电源</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6955482532911</t>
         </is>
       </c>
       <c r="L641" t="n">
+        <v>1</v>
+      </c>
+      <c r="M641" t="n">
         <v>1</v>
       </c>
       <c r="N641" t="n">
@@ -75869,17 +75869,17 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L642" t="n">
@@ -75937,17 +75937,17 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L643" t="n">
@@ -76005,17 +76005,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L644" t="n">
@@ -76149,12 +76149,12 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6927123810436</t>
         </is>
       </c>
       <c r="L646" t="n">
@@ -76220,12 +76220,12 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>6927123810436</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L647" t="n">
@@ -76433,12 +76433,12 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17 Air</t>
+          <t>MAGEASY iPhone 系列 Cryst M 超轻薄不发黄透明保护壳透明 iPhone 17 Air</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>6922329935969</t>
+          <t>4895241137464</t>
         </is>
       </c>
       <c r="L650" t="n">
@@ -76504,12 +76504,12 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>MAGEASY iPhone 系列 Cryst M 超轻薄不发黄透明保护壳透明 iPhone 17 Air</t>
+          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17 Air</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>4895241137464</t>
+          <t>6922329935969</t>
         </is>
       </c>
       <c r="L651" t="n">
@@ -76925,17 +76925,17 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 迪士尼 100 周年米奇保护壳 金色</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6975749267066</t>
         </is>
       </c>
       <c r="L657" t="n">
@@ -76996,17 +76996,17 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPhone 17 高清保护膜 透明</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>6978880670016</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L658" t="n">
@@ -77143,12 +77143,12 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 迪士尼 100 周年米奇保护壳 金色</t>
+          <t>RICHIC锐壳 iPhone 17 高清保护膜 透明</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>6975749267066</t>
+          <t>6978880670016</t>
         </is>
       </c>
       <c r="L660" t="n">
@@ -77209,17 +77209,17 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍视频</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>XMSY202612180</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L661" t="n">
@@ -77280,17 +77280,17 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍视频</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>XMSY202612180</t>
         </is>
       </c>
       <c r="L662" t="n">
@@ -77422,17 +77422,17 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>4894222083837</t>
         </is>
       </c>
       <c r="L664" t="n">
@@ -77569,12 +77569,12 @@
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L666" t="n">
@@ -77711,12 +77711,12 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>4894222083837</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L668" t="n">
@@ -77777,17 +77777,17 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L669" t="n">
@@ -78345,17 +78345,17 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>存储</t>
+          <t>iPad Air</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>LEXAR雷克沙 Professional Go 手机固态硬盘 银色 1T</t>
+          <t>13 英寸 iPad Air  M4 无线局域网机型 256GB - 紫色 - MH5X4CH/A</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>6977105652165</t>
+          <t>195****99330</t>
         </is>
       </c>
       <c r="L677" t="n">
@@ -78416,17 +78416,17 @@
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>iPad Air</t>
+          <t>存储</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>13 英寸 iPad Air  M4 无线局域网机型 256GB - 紫色 - MH5X4CH/A</t>
+          <t>LEXAR雷克沙 Professional Go 手机固态硬盘 银色 1T</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
         <is>
-          <t>195****99330</t>
+          <t>6977105652165</t>
         </is>
       </c>
       <c r="L678" t="n">
@@ -78634,18 +78634,15 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 2年版（Osmo Action 4）中国版</t>
+          <t>Osmo Action 4 标准套装</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>6941565963765</t>
+          <t>6941565965073</t>
         </is>
       </c>
       <c r="L681" t="n">
-        <v>1</v>
-      </c>
-      <c r="M681" t="n">
         <v>1</v>
       </c>
       <c r="N681" t="n">
@@ -78705,15 +78702,18 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>Osmo Action 4 标准套装</t>
+          <t>DJI Care 随心换 2年版（Osmo Action 4）中国版</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
         <is>
-          <t>6941565965073</t>
+          <t>6941565963765</t>
         </is>
       </c>
       <c r="L682" t="n">
+        <v>1</v>
+      </c>
+      <c r="M682" t="n">
         <v>1</v>
       </c>
       <c r="N682" t="n">
@@ -79049,20 +79049,23 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Action 4 全能套装</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6941565965080</t>
         </is>
       </c>
       <c r="L687" t="n">
+        <v>1</v>
+      </c>
+      <c r="M687" t="n">
         <v>1</v>
       </c>
       <c r="N687" t="n">
@@ -79117,23 +79120,20 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>Osmo Action 4 全能套装</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>6941565965080</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L688" t="n">
-        <v>1</v>
-      </c>
-      <c r="M688" t="n">
         <v>1</v>
       </c>
       <c r="N688" t="n">
@@ -79330,20 +79330,23 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo 时空凝固旋转手柄</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224122253</t>
         </is>
       </c>
       <c r="L691" t="n">
+        <v>1</v>
+      </c>
+      <c r="M691" t="n">
         <v>1</v>
       </c>
       <c r="N691" t="n">
@@ -79398,17 +79401,17 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>Osmo Action 双向 360° 腕带</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>6937224127739</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L692" t="n">
@@ -79466,23 +79469,20 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>Osmo 时空凝固旋转手柄</t>
+          <t>Osmo Action 双向 360° 腕带</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>6937224122253</t>
+          <t>6937224127739</t>
         </is>
       </c>
       <c r="L693" t="n">
-        <v>1</v>
-      </c>
-      <c r="M693" t="n">
         <v>1</v>
       </c>
       <c r="N693" t="n">
@@ -83036,23 +83036,20 @@
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>DJI礼包</t>
+          <t>保护膜</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>畅玩会员-99</t>
+          <t>X.ONE 大疆 Pocket 4 AR 增透保护膜</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>FHQLVIP0003</t>
+          <t>6937634522384</t>
         </is>
       </c>
       <c r="L744" t="n">
-        <v>1</v>
-      </c>
-      <c r="M744" t="n">
         <v>1</v>
       </c>
       <c r="N744" t="n">
@@ -83107,20 +83104,23 @@
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>保护膜</t>
+          <t>DJI礼包</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>X.ONE 大疆 Pocket 4 AR 增透保护膜</t>
+          <t>畅玩会员-99</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>6937634522384</t>
+          <t>FHQLVIP0003</t>
         </is>
       </c>
       <c r="L745" t="n">
+        <v>1</v>
+      </c>
+      <c r="M745" t="n">
         <v>1</v>
       </c>
       <c r="N745" t="n">
@@ -83246,17 +83246,17 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>遥控与控制</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>DJI Mic Mini 2 （手机版一发一收，含充电盒）</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224139770</t>
         </is>
       </c>
       <c r="L747" t="n">
@@ -83317,17 +83317,17 @@
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Nano</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Nano 随行套装</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224157705</t>
         </is>
       </c>
       <c r="L748" t="n">
@@ -83388,17 +83388,17 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>Nano</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>Osmo Nano 随行套装</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>6937224157705</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L749" t="n">
@@ -83459,17 +83459,17 @@
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>遥控与控制</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>DJI Mic Mini 2 （手机版一发一收，含充电盒）</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K750" t="inlineStr">
         <is>
-          <t>6937224139770</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L750" t="n">
@@ -83870,17 +83870,17 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>服务类</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>DJI RS 手柄延长脚架（金属版）</t>
+          <t>高阶升级礼包</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
         <is>
-          <t>6958265176142</t>
+          <t>DJI-0000003</t>
         </is>
       </c>
       <c r="L756" t="n">
@@ -83943,15 +83943,18 @@
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>Osmo 360 II 标准套装</t>
+          <t>Osmo 1.2 米隐形自拍杆套件</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>6937224148376</t>
+          <t>6937224118553</t>
         </is>
       </c>
       <c r="L757" t="n">
+        <v>1</v>
+      </c>
+      <c r="M757" t="n">
         <v>1</v>
       </c>
       <c r="N757" t="n">
@@ -84006,17 +84009,17 @@
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>雷克沙</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>雷克沙 Silver 极速TF存储卡Micro SD卡  512G</t>
+          <t>DJI RS 手柄延长脚架（金属版）</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
         <is>
-          <t>843367135400</t>
+          <t>6958265176142</t>
         </is>
       </c>
       <c r="L758" t="n">
@@ -84074,17 +84077,17 @@
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>DJI 晴雨伞（中国区）</t>
+          <t>DJI Care 随心换 2年版（Osmo 360 II）中国版</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
         <is>
-          <t>6941565984104</t>
+          <t>6937224154773</t>
         </is>
       </c>
       <c r="L759" t="n">
@@ -84142,17 +84145,17 @@
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>服务类</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>高阶升级礼包</t>
+          <t>Osmo 耐寒增强续航电池（2150 mAh）</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>DJI-0000003</t>
+          <t>6937224148833</t>
         </is>
       </c>
       <c r="L760" t="n">
@@ -84210,17 +84213,17 @@
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>雷克沙</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo 360 II）中国版</t>
+          <t>雷克沙 Silver 极速TF存储卡Micro SD卡  512G</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
         <is>
-          <t>6937224154889</t>
+          <t>843367135400</t>
         </is>
       </c>
       <c r="L761" t="n">
@@ -84283,12 +84286,12 @@
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>Osmo 耐寒增强续航电池（2150 mAh）</t>
+          <t>DJI Care 随心换 1年版（Osmo 360 II）中国版</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>6937224148833</t>
+          <t>6937224154889</t>
         </is>
       </c>
       <c r="L762" t="n">
@@ -84351,18 +84354,15 @@
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>Osmo 1.2 米隐形自拍杆套件</t>
+          <t>Osmo 360 II 标准套装</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>6937224118553</t>
+          <t>6937224148376</t>
         </is>
       </c>
       <c r="L763" t="n">
-        <v>1</v>
-      </c>
-      <c r="M763" t="n">
         <v>1</v>
       </c>
       <c r="N763" t="n">
@@ -84417,17 +84417,17 @@
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 2年版（Osmo 360 II）中国版</t>
+          <t>DJI 晴雨伞（中国区）</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
         <is>
-          <t>6937224154773</t>
+          <t>6941565984104</t>
         </is>
       </c>
       <c r="L764" t="n">
@@ -87869,17 +87869,17 @@
       </c>
       <c r="I813" t="inlineStr">
         <is>
-          <t>MateBook 数字</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>MateBook 14 MNTXM-24A(HarmonyOS 24GB+1TB) 触屏 樱粉金</t>
+          <t>礼品-配件-无线鼠标-CD20-R-黑色-55038737</t>
         </is>
       </c>
       <c r="K813" t="inlineStr">
         <is>
-          <t>6942103196201</t>
+          <t>A0890960</t>
         </is>
       </c>
       <c r="L813" t="n">
@@ -87940,17 +87940,17 @@
       </c>
       <c r="I814" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>MateBook 数字</t>
         </is>
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>礼品-配件-无线鼠标-CD20-R-黑色-55038737</t>
+          <t>MateBook 14 MNTXM-24A(HarmonyOS 24GB+1TB) 触屏 樱粉金</t>
         </is>
       </c>
       <c r="K814" t="inlineStr">
         <is>
-          <t>A0890960</t>
+          <t>6942103196201</t>
         </is>
       </c>
       <c r="L814" t="n">
@@ -88718,17 +88718,17 @@
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
         </is>
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****28869</t>
         </is>
       </c>
       <c r="L825" t="n">
@@ -88789,17 +88789,17 @@
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K826" t="inlineStr">
         <is>
-          <t>195****28869</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L826" t="n">
@@ -89428,17 +89428,17 @@
       </c>
       <c r="I835" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
+          <t>RICHIC锐壳 iPhone 17 Pro 高清保护膜 透明</t>
         </is>
       </c>
       <c r="K835" t="inlineStr">
         <is>
-          <t>6941876245437</t>
+          <t>6978880670030</t>
         </is>
       </c>
       <c r="L835" t="n">
@@ -89499,17 +89499,17 @@
       </c>
       <c r="I836" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J836" t="inlineStr">
         <is>
-          <t>NO1BOX IPhone 17 Pro 蜡笔小新多巴胺保护壳 向日葵班</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 深灰色</t>
         </is>
       </c>
       <c r="K836" t="inlineStr">
         <is>
-          <t>6923517323278</t>
+          <t>6928288527771</t>
         </is>
       </c>
       <c r="L836" t="n">
@@ -89570,17 +89570,17 @@
       </c>
       <c r="I837" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K837" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L837" t="n">
@@ -89641,17 +89641,17 @@
       </c>
       <c r="I838" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPhone 17 Pro 高清保护膜 透明</t>
+          <t>AppleCare Services for iPhone 17 Pro - SY7N2CH/A</t>
         </is>
       </c>
       <c r="K838" t="inlineStr">
         <is>
-          <t>6978880670030</t>
+          <t>195****10120</t>
         </is>
       </c>
       <c r="L838" t="n">
@@ -89712,17 +89712,17 @@
       </c>
       <c r="I839" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 深灰色</t>
+          <t>NO1BOX IPhone 17 Pro 蜡笔小新多巴胺保护壳 向日葵班</t>
         </is>
       </c>
       <c r="K839" t="inlineStr">
         <is>
-          <t>6928288527771</t>
+          <t>6923517323278</t>
         </is>
       </c>
       <c r="L839" t="n">
@@ -89783,17 +89783,17 @@
       </c>
       <c r="I840" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro - SY7N2CH/A</t>
+          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
         </is>
       </c>
       <c r="K840" t="inlineStr">
         <is>
-          <t>195****10120</t>
+          <t>6941876245437</t>
         </is>
       </c>
       <c r="L840" t="n">
@@ -89854,17 +89854,17 @@
       </c>
       <c r="I841" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K841" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L841" t="n">
@@ -89996,17 +89996,17 @@
       </c>
       <c r="I843" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>LIBRATONE小鸟音响 UP 耳机 莺眉黄</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K843" t="inlineStr">
         <is>
-          <t>6975324441119</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L843" t="n">
@@ -90067,17 +90067,17 @@
       </c>
       <c r="I844" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPhone 17 Pro 透明磨砂保护壳 透明</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K844" t="inlineStr">
         <is>
-          <t>6978880670146</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L844" t="n">
@@ -90138,17 +90138,17 @@
       </c>
       <c r="I845" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>LIBRATONE小鸟音响 UP 耳机 莺眉黄</t>
         </is>
       </c>
       <c r="K845" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6975324441119</t>
         </is>
       </c>
       <c r="L845" t="n">
@@ -90209,17 +90209,17 @@
       </c>
       <c r="I846" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>RICHIC锐壳 iPhone 17 Pro 透明磨砂保护壳 透明</t>
         </is>
       </c>
       <c r="K846" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6978880670146</t>
         </is>
       </c>
       <c r="L846" t="n">
@@ -91865,17 +91865,17 @@
       </c>
       <c r="I870" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J870" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo 360 II）中国版</t>
+          <t>DJI 渐变色运动水杯（中国区）</t>
         </is>
       </c>
       <c r="K870" t="inlineStr">
         <is>
-          <t>6937224154889</t>
+          <t>6941565984128</t>
         </is>
       </c>
       <c r="L870" t="n">
@@ -91936,17 +91936,17 @@
       </c>
       <c r="I871" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>DJI RS 手柄延长脚架（金属版）</t>
+          <t>Osmo 可调节快拆转接件</t>
         </is>
       </c>
       <c r="K871" t="inlineStr">
         <is>
-          <t>6958265176142</t>
+          <t>6937224114678</t>
         </is>
       </c>
       <c r="L871" t="n">
@@ -92012,12 +92012,12 @@
       </c>
       <c r="J872" t="inlineStr">
         <is>
-          <t>Osmo 360 II 标准套装</t>
+          <t>DJI Care 随心换 1年版（Osmo 360 II）中国版</t>
         </is>
       </c>
       <c r="K872" t="inlineStr">
         <is>
-          <t>6937224148376</t>
+          <t>6937224154889</t>
         </is>
       </c>
       <c r="L872" t="n">
@@ -92149,17 +92149,17 @@
       </c>
       <c r="I874" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J874" t="inlineStr">
         <is>
-          <t>DJI 渐变色运动水杯（中国区）</t>
+          <t>Osmo 360 II 标准套装</t>
         </is>
       </c>
       <c r="K874" t="inlineStr">
         <is>
-          <t>6941565984128</t>
+          <t>6937224148376</t>
         </is>
       </c>
       <c r="L874" t="n">
@@ -92220,17 +92220,17 @@
       </c>
       <c r="I875" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>Osmo 可调节快拆转接件</t>
+          <t>DJI RS 手柄延长脚架（金属版）</t>
         </is>
       </c>
       <c r="K875" t="inlineStr">
         <is>
-          <t>6937224114678</t>
+          <t>6958265176142</t>
         </is>
       </c>
       <c r="L875" t="n">
@@ -93287,12 +93287,12 @@
       </c>
       <c r="J890" t="inlineStr">
         <is>
-          <t>ROMO 清洁配件套装 (DJI ROMO P\A系列) (全球)</t>
+          <t>DJI ROMO P2 扫地机器人 (超薄上下水版) (中国大陆)</t>
         </is>
       </c>
       <c r="K890" t="inlineStr">
         <is>
-          <t>6937224155411</t>
+          <t>6937224155428</t>
         </is>
       </c>
       <c r="L890" t="n">
@@ -93358,12 +93358,12 @@
       </c>
       <c r="J891" t="inlineStr">
         <is>
-          <t>DJI ROMO P2 扫地机器人 (超薄上下水版) (中国大陆)</t>
+          <t>ROMO 清洁配件套装 (DJI ROMO P\A系列) (全球)</t>
         </is>
       </c>
       <c r="K891" t="inlineStr">
         <is>
-          <t>6937224155428</t>
+          <t>6937224155411</t>
         </is>
       </c>
       <c r="L891" t="n">
@@ -93429,12 +93429,12 @@
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 2年版（Osmo Pocket 4P）中国版</t>
+          <t>Osmo 迷你三脚架</t>
         </is>
       </c>
       <c r="K892" t="inlineStr">
         <is>
-          <t>6937224150911</t>
+          <t>6941565969811</t>
         </is>
       </c>
       <c r="L892" t="n">
@@ -93495,17 +93495,17 @@
       </c>
       <c r="I893" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Pocket</t>
         </is>
       </c>
       <c r="J893" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>DJI Care 随心换 2年版（Osmo Pocket 4P）中国版</t>
         </is>
       </c>
       <c r="K893" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224150911</t>
         </is>
       </c>
       <c r="L893" t="n">
@@ -93637,17 +93637,17 @@
       </c>
       <c r="I895" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J895" t="inlineStr">
         <is>
-          <t>Osmo 迷你三脚架</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K895" t="inlineStr">
         <is>
-          <t>6941565969811</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L895" t="n">
@@ -95823,17 +95823,17 @@
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J926" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 经典磁吸保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K926" t="inlineStr">
         <is>
-          <t>6927123811631</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L926" t="n">
@@ -95894,17 +95894,17 @@
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J927" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>iPhone 17 Pro Max 512GB 星宇橙色 - MG074CH/A</t>
         </is>
       </c>
       <c r="K927" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>195****41158</t>
         </is>
       </c>
       <c r="L927" t="n">
@@ -96036,17 +96036,17 @@
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J929" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 经典磁吸保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K929" t="inlineStr">
         <is>
-          <t>6927123811631</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L929" t="n">
@@ -96107,17 +96107,17 @@
       </c>
       <c r="I930" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J930" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>ZGA iPhone 系列 经典磁吸保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K930" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6927123811631</t>
         </is>
       </c>
       <c r="L930" t="n">
@@ -96183,12 +96183,12 @@
       </c>
       <c r="J931" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 经典磁吸保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K931" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6927123811631</t>
         </is>
       </c>
       <c r="L931" t="n">
@@ -96249,17 +96249,17 @@
       </c>
       <c r="I932" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J932" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 512GB 星宇橙色 - MG074CH/A</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K932" t="inlineStr">
         <is>
-          <t>195****41158</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L932" t="n">
@@ -96320,17 +96320,17 @@
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J933" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K933" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L933" t="n">
@@ -96533,17 +96533,17 @@
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K936" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L936" t="n">
@@ -96675,17 +96675,17 @@
       </c>
       <c r="I938" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J938" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K938" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L938" t="n">
@@ -96751,12 +96751,12 @@
       </c>
       <c r="J939" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 明透磁吸保护壳 透明 iPhone 17</t>
+          <t>ZGA iPhone 系列 明透磁吸保护壳 透明 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K939" t="inlineStr">
         <is>
-          <t>6927123809904</t>
+          <t>6927123809935</t>
         </is>
       </c>
       <c r="L939" t="n">
@@ -96814,23 +96814,20 @@
       </c>
       <c r="I940" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J940" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPhone 系列 织界系列凯夫拉磁吸保护壳 见山 iPhone 17 Pro Max</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K940" t="inlineStr">
         <is>
-          <t>6942297133914</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L940" t="n">
-        <v>1</v>
-      </c>
-      <c r="M940" t="n">
         <v>1</v>
       </c>
       <c r="N940" t="n">
@@ -96890,15 +96887,18 @@
       </c>
       <c r="J941" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>COMMA珂玛 iPhone 系列 织界系列凯夫拉磁吸保护壳 见山 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K941" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6942297133914</t>
         </is>
       </c>
       <c r="L941" t="n">
+        <v>1</v>
+      </c>
+      <c r="M941" t="n">
         <v>1</v>
       </c>
       <c r="N941" t="n">
@@ -96953,17 +96953,17 @@
       </c>
       <c r="I942" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J942" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K942" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L942" t="n">
@@ -97094,12 +97094,12 @@
       </c>
       <c r="J944" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 明透磁吸保护壳 透明 iPhone 17 Pro Max</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K944" t="inlineStr">
         <is>
-          <t>6927123809935</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L944" t="n">
@@ -97157,17 +97157,17 @@
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J945" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>ZGA iPhone 系列 明透磁吸保护壳 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K945" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>6927123809904</t>
         </is>
       </c>
       <c r="L945" t="n">
@@ -97225,17 +97225,17 @@
       </c>
       <c r="I946" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J946" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K946" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L946" t="n">
@@ -97298,12 +97298,12 @@
       </c>
       <c r="J947" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K947" t="inlineStr">
         <is>
-          <t>6955482539514</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L947" t="n">
@@ -97369,12 +97369,12 @@
       </c>
       <c r="J948" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
         </is>
       </c>
       <c r="K948" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6955482539514</t>
         </is>
       </c>
       <c r="L948" t="n">
@@ -97577,17 +97577,17 @@
       </c>
       <c r="I951" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J951" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K951" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L951" t="n">
@@ -97653,12 +97653,12 @@
       </c>
       <c r="J952" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 明透磁吸保护壳 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K952" t="inlineStr">
         <is>
-          <t>6927123810375</t>
+          <t>6927123809904</t>
         </is>
       </c>
       <c r="L952" t="n">
@@ -97724,12 +97724,12 @@
       </c>
       <c r="J953" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA iPhone 17 Pro 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K953" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123810375</t>
         </is>
       </c>
       <c r="L953" t="n">
@@ -97790,17 +97790,17 @@
       </c>
       <c r="I954" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J954" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 明透磁吸保护壳 透明 iPhone 17</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K954" t="inlineStr">
         <is>
-          <t>6927123809904</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L954" t="n">
@@ -97932,17 +97932,17 @@
       </c>
       <c r="I956" t="inlineStr">
         <is>
-          <t>运营商</t>
+          <t>MacBook Air</t>
         </is>
       </c>
       <c r="J956" t="inlineStr">
         <is>
-          <t>(U享套餐）流量王畅享159元子产品24期</t>
+          <t>13 英寸 MacBook Air: Apple M1 芯片，配备 8 核中央处理器和 7 核图形处理器, 256GB SSD - 银色-MGN93CH/A</t>
         </is>
       </c>
       <c r="K956" t="inlineStr">
         <is>
-          <t>LTHF-UXTC-159-24</t>
+          <t>194****57223</t>
         </is>
       </c>
       <c r="L956" t="n">
@@ -98003,17 +98003,17 @@
       </c>
       <c r="I957" t="inlineStr">
         <is>
-          <t>MacBook Air</t>
+          <t>运营商</t>
         </is>
       </c>
       <c r="J957" t="inlineStr">
         <is>
-          <t>13 英寸 MacBook Air: Apple M1 芯片，配备 8 核中央处理器和 7 核图形处理器, 256GB SSD - 银色-MGN93CH/A</t>
+          <t>(U享套餐）流量王畅享159元子产品24期</t>
         </is>
       </c>
       <c r="K957" t="inlineStr">
         <is>
-          <t>194****57223</t>
+          <t>LTHF-UXTC-159-24</t>
         </is>
       </c>
       <c r="L957" t="n">
@@ -98647,12 +98647,12 @@
       </c>
       <c r="J966" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K966" t="inlineStr">
         <is>
-          <t>6942297127029</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L966" t="n">
@@ -98713,17 +98713,17 @@
       </c>
       <c r="I967" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J967" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K967" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L967" t="n">
@@ -98784,17 +98784,17 @@
       </c>
       <c r="I968" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J968" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K968" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6942297127029</t>
         </is>
       </c>
       <c r="L968" t="n">
@@ -98926,17 +98926,17 @@
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>运营商</t>
         </is>
       </c>
       <c r="J970" t="inlineStr">
         <is>
-          <t>16 英寸 MacBook Pro: Apple M4 Pro 芯片，配备 14 核中央处理器和 20 核图形处理器, 24GB, 512GB SSD - 深空黑色-MX2X3CH/A</t>
+          <t>成都区域-（当月）-橙分期单C-天翼畅享39橙分期套餐返16-返还期数36个月-购机直降480元-预存300元话费</t>
         </is>
       </c>
       <c r="K970" t="inlineStr">
         <is>
-          <t>195****69433</t>
+          <t>FWL-CDQY-0011</t>
         </is>
       </c>
       <c r="L970" t="n">
@@ -98997,17 +98997,17 @@
       </c>
       <c r="I971" t="inlineStr">
         <is>
-          <t>运营商</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="J971" t="inlineStr">
         <is>
-          <t>成都区域-（当月）-橙分期单C-天翼畅享39橙分期套餐返16-返还期数36个月-购机直降480元-预存300元话费</t>
+          <t>16 英寸 MacBook Pro: Apple M4 Pro 芯片，配备 14 核中央处理器和 20 核图形处理器, 24GB, 512GB SSD - 深空黑色-MX2X3CH/A</t>
         </is>
       </c>
       <c r="K971" t="inlineStr">
         <is>
-          <t>FWL-CDQY-0011</t>
+          <t>195****69433</t>
         </is>
       </c>
       <c r="L971" t="n">
@@ -99139,17 +99139,17 @@
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>Nano</t>
+          <t>遥控与控制</t>
         </is>
       </c>
       <c r="J973" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 2年版（Osmo Nano）中国版</t>
+          <t>DJI Mic Mini 2 （两发一收，含充电盒）</t>
         </is>
       </c>
       <c r="K973" t="inlineStr">
         <is>
-          <t>6937224116054</t>
+          <t>6937224139749</t>
         </is>
       </c>
       <c r="L973" t="n">
@@ -99210,17 +99210,17 @@
       </c>
       <c r="I974" t="inlineStr">
         <is>
-          <t>雷克沙</t>
+          <t>Nano</t>
         </is>
       </c>
       <c r="J974" t="inlineStr">
         <is>
-          <t>雷克沙 Silver 极速TF存储卡Micro SD卡  512G</t>
+          <t>Osmo Nano 随行套装</t>
         </is>
       </c>
       <c r="K974" t="inlineStr">
         <is>
-          <t>843367135400</t>
+          <t>6937224157705</t>
         </is>
       </c>
       <c r="L974" t="n">
@@ -99286,12 +99286,12 @@
       </c>
       <c r="J975" t="inlineStr">
         <is>
-          <t>Osmo Nano 随行套装</t>
+          <t>DJI Care 随心换 1年版（Osmo Nano）中国版</t>
         </is>
       </c>
       <c r="K975" t="inlineStr">
         <is>
-          <t>6937224157705</t>
+          <t>6937224116146</t>
         </is>
       </c>
       <c r="L975" t="n">
@@ -99352,17 +99352,17 @@
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>Nano</t>
+          <t>雷克沙</t>
         </is>
       </c>
       <c r="J976" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Nano）中国版</t>
+          <t>雷克沙 Silver 极速TF存储卡Micro SD卡  512G</t>
         </is>
       </c>
       <c r="K976" t="inlineStr">
         <is>
-          <t>6937224116146</t>
+          <t>843367135400</t>
         </is>
       </c>
       <c r="L976" t="n">
@@ -99423,17 +99423,17 @@
       </c>
       <c r="I977" t="inlineStr">
         <is>
-          <t>遥控与控制</t>
+          <t>Nano</t>
         </is>
       </c>
       <c r="J977" t="inlineStr">
         <is>
-          <t>DJI Mic Mini 2 （两发一收，含充电盒）</t>
+          <t>DJI Care 随心换 2年版（Osmo Nano）中国版</t>
         </is>
       </c>
       <c r="K977" t="inlineStr">
         <is>
-          <t>6937224139749</t>
+          <t>6937224116054</t>
         </is>
       </c>
       <c r="L977" t="n">
@@ -100547,17 +100547,17 @@
       </c>
       <c r="I993" t="inlineStr">
         <is>
-          <t>保护膜</t>
+          <t>DJI礼包</t>
         </is>
       </c>
       <c r="J993" t="inlineStr">
         <is>
-          <t>X.ONE 大疆 Pocket 4 AR 增透保护膜</t>
+          <t>畅玩会员-99</t>
         </is>
       </c>
       <c r="K993" t="inlineStr">
         <is>
-          <t>6937634522384</t>
+          <t>FHQLVIP0003</t>
         </is>
       </c>
       <c r="L993" t="n">
@@ -100618,17 +100618,17 @@
       </c>
       <c r="I994" t="inlineStr">
         <is>
-          <t>DJI礼包</t>
+          <t>保护膜</t>
         </is>
       </c>
       <c r="J994" t="inlineStr">
         <is>
-          <t>畅玩会员-99</t>
+          <t>X.ONE 大疆 Pocket 4 AR 增透保护膜</t>
         </is>
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>FHQLVIP0003</t>
+          <t>6937634522384</t>
         </is>
       </c>
       <c r="L994" t="n">
@@ -100901,19 +100901,19 @@
       </c>
       <c r="J998" t="inlineStr">
         <is>
-          <t>新版折扣合约-5G全家享189套餐24个月（话费预存版）</t>
+          <t>电信话费充值</t>
         </is>
       </c>
       <c r="K998" t="inlineStr">
         <is>
-          <t>FWL10010132</t>
+          <t>HW030208</t>
         </is>
       </c>
       <c r="L998" t="n">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="M998" t="n">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="N998" t="n">
         <v>240000</v>
@@ -100972,19 +100972,19 @@
       </c>
       <c r="J999" t="inlineStr">
         <is>
-          <t>电信话费充值</t>
+          <t>新版折扣合约-5G全家享189套餐24个月（话费预存版）</t>
         </is>
       </c>
       <c r="K999" t="inlineStr">
         <is>
-          <t>HW030208</t>
+          <t>FWL10010132</t>
         </is>
       </c>
       <c r="L999" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="M999" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="N999" t="n">
         <v>240000</v>
@@ -101177,23 +101177,20 @@
       </c>
       <c r="I1002" t="inlineStr">
         <is>
-          <t>FreeClip</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J1002" t="inlineStr">
         <is>
-          <t>FreeClip 2 典藏版 无线耳机 T0027 星海蓝</t>
+          <t>礼品-定制-音频Freeclip 2配饰-花点心思</t>
         </is>
       </c>
       <c r="K1002" t="inlineStr">
         <is>
-          <t>6942103196768</t>
+          <t>A0800889</t>
         </is>
       </c>
       <c r="L1002" t="n">
-        <v>1</v>
-      </c>
-      <c r="M1002" t="n">
         <v>1</v>
       </c>
       <c r="N1002" t="n">
@@ -101248,23 +101245,20 @@
       </c>
       <c r="I1003" t="inlineStr">
         <is>
-          <t>FreeClip</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J1003" t="inlineStr">
         <is>
-          <t>FreeClip 2 典藏版 无线耳机 T0027 星海蓝</t>
+          <t>礼品-定制-音频Freeclip 2配饰-花点心思</t>
         </is>
       </c>
       <c r="K1003" t="inlineStr">
         <is>
-          <t>6942103196768</t>
+          <t>A0800889</t>
         </is>
       </c>
       <c r="L1003" t="n">
-        <v>1</v>
-      </c>
-      <c r="M1003" t="n">
         <v>1</v>
       </c>
       <c r="N1003" t="n">
@@ -101461,20 +101455,23 @@
       </c>
       <c r="I1006" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>FreeClip</t>
         </is>
       </c>
       <c r="J1006" t="inlineStr">
         <is>
-          <t>礼品-定制-音频Freeclip 2配饰-花点心思</t>
+          <t>FreeClip 2 典藏版 无线耳机 T0027 星海蓝</t>
         </is>
       </c>
       <c r="K1006" t="inlineStr">
         <is>
-          <t>A0800889</t>
+          <t>6942103196768</t>
         </is>
       </c>
       <c r="L1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1006" t="n">
         <v>1</v>
       </c>
       <c r="N1006" t="n">
@@ -101529,20 +101526,23 @@
       </c>
       <c r="I1007" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>FreeClip</t>
         </is>
       </c>
       <c r="J1007" t="inlineStr">
         <is>
-          <t>礼品-定制-音频Freeclip 2配饰-花点心思</t>
+          <t>FreeClip 2 典藏版 无线耳机 T0027 星海蓝</t>
         </is>
       </c>
       <c r="K1007" t="inlineStr">
         <is>
-          <t>A0800889</t>
+          <t>6942103196768</t>
         </is>
       </c>
       <c r="L1007" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1007" t="n">
         <v>1</v>
       </c>
       <c r="N1007" t="n">
